--- a/artfynd/A 20315-2026 artfynd.xlsx
+++ b/artfynd/A 20315-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132617550</v>
       </c>
       <c r="B2" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>132623261</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>132623253</v>
       </c>
       <c r="B4" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20315-2026 artfynd.xlsx
+++ b/artfynd/A 20315-2026 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>132623253</v>
       </c>
       <c r="B4" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20315-2026 artfynd.xlsx
+++ b/artfynd/A 20315-2026 artfynd.xlsx
@@ -790,37 +790,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132623261</v>
+        <v>132623253</v>
       </c>
       <c r="B3" t="n">
-        <v>79328</v>
+        <v>101330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672904</v>
+        <v>672918</v>
       </c>
       <c r="R3" t="n">
-        <v>6981255</v>
+        <v>6980944</v>
       </c>
       <c r="S3" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,42 +906,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132623253</v>
+        <v>132623261</v>
       </c>
       <c r="B4" t="n">
-        <v>101329</v>
+        <v>79329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672918</v>
+        <v>672904</v>
       </c>
       <c r="R4" t="n">
-        <v>6980944</v>
+        <v>6981255</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20315-2026 artfynd.xlsx
+++ b/artfynd/A 20315-2026 artfynd.xlsx
@@ -790,42 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132623253</v>
+        <v>132623261</v>
       </c>
       <c r="B3" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672918</v>
+        <v>672904</v>
       </c>
       <c r="R3" t="n">
-        <v>6980944</v>
+        <v>6981255</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,37 +901,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132623261</v>
+        <v>132623253</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672904</v>
+        <v>672918</v>
       </c>
       <c r="R4" t="n">
-        <v>6981255</v>
+        <v>6980944</v>
       </c>
       <c r="S4" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20315-2026 artfynd.xlsx
+++ b/artfynd/A 20315-2026 artfynd.xlsx
@@ -790,37 +790,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132623261</v>
+        <v>132623253</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672904</v>
+        <v>672918</v>
       </c>
       <c r="R3" t="n">
-        <v>6981255</v>
+        <v>6980944</v>
       </c>
       <c r="S3" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,42 +906,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132623253</v>
+        <v>132623261</v>
       </c>
       <c r="B4" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672918</v>
+        <v>672904</v>
       </c>
       <c r="R4" t="n">
-        <v>6980944</v>
+        <v>6981255</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 20315-2026 artfynd.xlsx
+++ b/artfynd/A 20315-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132617551</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132617548</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623261</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623270</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132617549</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132617564</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1487,6 +1522,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132617565</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1602,6 +1642,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132617550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1754,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132617553</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1825,6 +1875,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623253</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1941,6 +1996,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623254</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2057,8 +2117,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623268</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>